--- a/desguace/REDI.xlsx
+++ b/desguace/REDI.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X61"/>
+  <dimension ref="A1:X88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5715,6 +5715,2304 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="b">
+        <v>0</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>5016480</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Limpieza de sentina</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>45981</v>
+      </c>
+      <c r="F62" t="n">
+        <v>38505922</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>32022290</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>DETERGENTE IND.</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>5</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>5</v>
+      </c>
+      <c r="L62" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="M62" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>@01@</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>REDI020596</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="b">
+        <v>0</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>5016480</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Limpieza de sentina</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>45981</v>
+      </c>
+      <c r="F63" t="n">
+        <v>38505922</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>32005362</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>TRAPO IND.</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>5</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>5</v>
+      </c>
+      <c r="L63" t="n">
+        <v>12</v>
+      </c>
+      <c r="M63" t="n">
+        <v>12</v>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>@01@</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>REDI020596</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="b">
+        <v>0</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>5016480</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Limpieza de tanque petróleo</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>45974</v>
+      </c>
+      <c r="F64" t="n">
+        <v>38505922</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>32005362</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>TRAPO IND.</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>20</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>20</v>
+      </c>
+      <c r="L64" t="n">
+        <v>48</v>
+      </c>
+      <c r="M64" t="n">
+        <v>48</v>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>@01@</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>REDI020591</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="b">
+        <v>0</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>5016480</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Limpieza de tanque petróleo</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>45974</v>
+      </c>
+      <c r="F65" t="n">
+        <v>38505922</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>32022290</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>DETERGENTE IND.</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>20</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>20</v>
+      </c>
+      <c r="L65" t="n">
+        <v>118</v>
+      </c>
+      <c r="M65" t="n">
+        <v>118</v>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>@01@</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>REDI020591</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="b">
+        <v>0</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>5016486</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Desm de accesorias de sistemas auxiliar</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>45980</v>
+      </c>
+      <c r="F66" t="n">
+        <v>38512616</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>31009820</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>DISCO CORTE FE.1/8"X7/8"X4 1/2"</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>10</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>10</v>
+      </c>
+      <c r="L66" t="n">
+        <v>29.87</v>
+      </c>
+      <c r="M66" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>@01@</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>REDI020606</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="b">
+        <v>0</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>5016486</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Desm de accesorias de sistemas auxiliar</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>45980</v>
+      </c>
+      <c r="F67" t="n">
+        <v>38512616</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>31009817</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>DISCO CORTE FE.0.04"X7/8"X4 1/2"</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>10</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>10</v>
+      </c>
+      <c r="L67" t="n">
+        <v>29.16</v>
+      </c>
+      <c r="M67" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>@01@</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>REDI020606</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="b">
+        <v>0</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>5016486</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Desm de accesorias de sistemas auxiliar</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>45980</v>
+      </c>
+      <c r="F68" t="n">
+        <v>38512616</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>31003986</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>OXIGENO IND.</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>20</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>20</v>
+      </c>
+      <c r="L68" t="n">
+        <v>190</v>
+      </c>
+      <c r="M68" t="n">
+        <v>149</v>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>@01@</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>REDI020606</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="b">
+        <v>0</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>5016486</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Desm de accesorias de sistemas auxiliar</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>45980</v>
+      </c>
+      <c r="F69" t="n">
+        <v>38512616</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>31010776</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>GAS PROPANO 10KG</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>BOT</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>1</v>
+      </c>
+      <c r="L69" t="n">
+        <v>53.73</v>
+      </c>
+      <c r="M69" t="n">
+        <v>53.73</v>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>@01@</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>REDI020606</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="b">
+        <v>0</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>5016486</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>0040</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Desm y evacuación</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>46009</v>
+      </c>
+      <c r="F70" t="n">
+        <v>38512616</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>31003986</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>OXIGENO IND.</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>30</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>30</v>
+      </c>
+      <c r="L70" t="n">
+        <v>285</v>
+      </c>
+      <c r="M70" t="n">
+        <v>223.5</v>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="b">
+        <v>0</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>5016486</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>0040</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Desm y evacuación</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>46016</v>
+      </c>
+      <c r="F71" t="n">
+        <v>38512616</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>31010776</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>GAS PROPANO 10KG</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>BOT</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>1</v>
+      </c>
+      <c r="L71" t="n">
+        <v>53.73</v>
+      </c>
+      <c r="M71" t="n">
+        <v>53.73</v>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>@01@</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>REDI020857</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="b">
+        <v>0</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>5016486</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>0040</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Desm y evacuación</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>46009</v>
+      </c>
+      <c r="F72" t="n">
+        <v>38512616</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>31013874</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>SOLDADURA SUPERCITO E7018 3.25MM 25KG</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>6</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>KG</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>6</v>
+      </c>
+      <c r="L72" t="n">
+        <v>61.22</v>
+      </c>
+      <c r="M72" t="n">
+        <v>60.66</v>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="b">
+        <v>0</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>5016486</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>0040</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Desm y evacuación</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>46016</v>
+      </c>
+      <c r="F73" t="n">
+        <v>38512616</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>31003986</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>OXIGENO IND.</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>20</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>20</v>
+      </c>
+      <c r="L73" t="n">
+        <v>190</v>
+      </c>
+      <c r="M73" t="n">
+        <v>149</v>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>@01@</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>REDI020857</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="b">
+        <v>0</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>5016486</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>0040</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Desm y evacuación</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>46009</v>
+      </c>
+      <c r="F74" t="n">
+        <v>38512616</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>31010776</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>GAS PROPANO 10KG</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>1</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>BOT</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L74" t="n">
+        <v>53.73</v>
+      </c>
+      <c r="M74" t="n">
+        <v>53.73</v>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="b">
+        <v>0</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>5016487</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Desmontaje desaguadores y colectores</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>46013</v>
+      </c>
+      <c r="F75" t="n">
+        <v>38512617</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>31003986</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>OXIGENO IND.</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>40</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>40</v>
+      </c>
+      <c r="L75" t="n">
+        <v>380</v>
+      </c>
+      <c r="M75" t="n">
+        <v>298</v>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>@01@</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>REDI020836</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="b">
+        <v>0</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>5016487</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Desmontaje desaguadores y colectores</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>46013</v>
+      </c>
+      <c r="F76" t="n">
+        <v>38512617</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>31010776</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>GAS PROPANO 10KG</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>2</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>BOT</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>2</v>
+      </c>
+      <c r="L76" t="n">
+        <v>107.46</v>
+      </c>
+      <c r="M76" t="n">
+        <v>107.46</v>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>@01@</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>REDI020836</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="b">
+        <v>0</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>5016545</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Calderería para SP/SG</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>45975</v>
+      </c>
+      <c r="F77" t="n">
+        <v>38739694</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>31010776</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>GAS PROPANO 10KG</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>BOT</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" t="n">
+        <v>53.73</v>
+      </c>
+      <c r="M77" t="n">
+        <v>53.73</v>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>@01@</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>REDI020592</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="b">
+        <v>0</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>5016545</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Calderería para SP/SG</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>45975</v>
+      </c>
+      <c r="F78" t="n">
+        <v>38739694</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>31003986</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>OXIGENO IND.</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>10</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>10</v>
+      </c>
+      <c r="L78" t="n">
+        <v>95</v>
+      </c>
+      <c r="M78" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>@01@</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>REDI020592</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="b">
+        <v>0</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>5016553</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Desguace estructura</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>46017</v>
+      </c>
+      <c r="F79" t="n">
+        <v>38757821</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>31003986</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>OXIGENO IND.</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>120</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>120</v>
+      </c>
+      <c r="L79" t="n">
+        <v>1140</v>
+      </c>
+      <c r="M79" t="n">
+        <v>894</v>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>@01@</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>REDI020941</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>SISTEMAS AUXILIARES</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="b">
+        <v>0</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>5016553</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Desguace estructura</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>46023</v>
+      </c>
+      <c r="F80" t="n">
+        <v>38757821</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>31003986</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>OXIGENO IND.</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>100</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>100</v>
+      </c>
+      <c r="L80" t="n">
+        <v>950</v>
+      </c>
+      <c r="M80" t="n">
+        <v>745</v>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>@01@</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>REDI020941</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>SISTEMAS AUXILIARES</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="b">
+        <v>0</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>5016553</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Desguace estructura</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="F81" t="n">
+        <v>38757821</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>31003986</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>OXIGENO IND.</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>200</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>200</v>
+      </c>
+      <c r="L81" t="n">
+        <v>1900</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1490</v>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>@01@</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>REDI020941</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>SISTEMAS AUXILIARES</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="b">
+        <v>0</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>5016553</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Desguace estructura</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>46032</v>
+      </c>
+      <c r="F82" t="n">
+        <v>38757821</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>31003986</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>OXIGENO IND.</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>100</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>100</v>
+      </c>
+      <c r="L82" t="n">
+        <v>950</v>
+      </c>
+      <c r="M82" t="n">
+        <v>745</v>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>@01@</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>REDI020941</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>SISTEMAS AUXILIARES</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="b">
+        <v>0</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>5016553</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Desguace estructura</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>46034</v>
+      </c>
+      <c r="F83" t="n">
+        <v>38757821</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>31003986</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>OXIGENO IND.</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>100</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>100</v>
+      </c>
+      <c r="L83" t="n">
+        <v>950</v>
+      </c>
+      <c r="M83" t="n">
+        <v>745</v>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>@01@</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>REDI020941</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>SISTEMAS AUXILIARES</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="b">
+        <v>0</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>5016553</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Desguace estructura</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>46032</v>
+      </c>
+      <c r="F84" t="n">
+        <v>38757821</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>31010776</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>GAS PROPANO 10KG</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>3</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>BOT</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>161.19</v>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>@01@</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>REDI020941</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>SISTEMAS AUXILIARES</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="b">
+        <v>0</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>5016553</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Desguace estructura</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>46016</v>
+      </c>
+      <c r="F85" t="n">
+        <v>38757821</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>31010776</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>GAS PROPANO 10KG</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>4</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>BOT</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>4</v>
+      </c>
+      <c r="L85" t="n">
+        <v>214.92</v>
+      </c>
+      <c r="M85" t="n">
+        <v>214.92</v>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>@01@</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>REDI020941</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>SISTEMAS AUXILIARES</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="b">
+        <v>0</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>5016553</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Desguace estructura</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>46017</v>
+      </c>
+      <c r="F86" t="n">
+        <v>38757821</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>31010776</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>GAS PROPANO 10KG</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>6</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>BOT</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>6</v>
+      </c>
+      <c r="L86" t="n">
+        <v>322.38</v>
+      </c>
+      <c r="M86" t="n">
+        <v>322.38</v>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>@01@</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>REDI020941</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>SISTEMAS AUXILIARES</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="b">
+        <v>0</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>5016553</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Desguace estructura</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="F87" t="n">
+        <v>38757821</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>31010776</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>GAS PROPANO 10KG</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>6</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>BOT</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>6</v>
+      </c>
+      <c r="L87" t="n">
+        <v>322.38</v>
+      </c>
+      <c r="M87" t="n">
+        <v>322.38</v>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>@01@</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>REDI020941</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>SISTEMAS AUXILIARES</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="b">
+        <v>0</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>5016553</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Desguace estructura</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>46016</v>
+      </c>
+      <c r="F88" t="n">
+        <v>38757821</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>31003986</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>OXIGENO IND.</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>70</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>70</v>
+      </c>
+      <c r="L88" t="n">
+        <v>665</v>
+      </c>
+      <c r="M88" t="n">
+        <v>521.5</v>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>@01@</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>REDI020941</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>SISTEMAS AUXILIARES</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
